--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-contact-relationship-category.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-contact-relationship-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-05T12:16:59+00:00</t>
+    <t>2026-06-05T12:18:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-contact-relationship-category.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-contact-relationship-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-05T12:18:27+00:00</t>
+    <t>2026-06-05T12:21:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-contact-relationship-category.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-contact-relationship-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-05T12:21:59+00:00</t>
+    <t>2026-06-05T13:35:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-contact-relationship-category.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-contact-relationship-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-05T13:35:06+00:00</t>
+    <t>2026-08-04T12:27:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-contact-relationship-category.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-contact-relationship-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:27:17+00:00</t>
+    <t>2026-08-04T15:42:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-contact-relationship-category.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-contact-relationship-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T15:42:07+00:00</t>
+    <t>2026-08-07T07:47:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-contact-relationship-category.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-contact-relationship-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T07:47:42+00:00</t>
+    <t>2026-08-07T08:01:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-contact-relationship-category.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-contact-relationship-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T08:01:10+00:00</t>
+    <t>2026-08-07T08:58:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-contact-relationship-category.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-contact-relationship-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T08:58:25+00:00</t>
+    <t>2026-08-07T11:55:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-contact-relationship-category.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-contact-relationship-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T11:55:57+00:00</t>
+    <t>2026-08-10T12:42:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-contact-relationship-category.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-contact-relationship-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T12:42:53+00:00</t>
+    <t>2026-08-10T13:14:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-contact-relationship-category.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-contact-relationship-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T13:14:57+00:00</t>
+    <t>2026-08-10T13:29:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-contact-relationship-category.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-contact-relationship-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T13:29:34+00:00</t>
+    <t>2026-08-10T13:33:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-contact-relationship-category.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-contact-relationship-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T13:33:35+00:00</t>
+    <t>2026-08-10T13:39:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-contact-relationship-category.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-contact-relationship-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T13:39:12+00:00</t>
+    <t>2026-08-10T13:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-contact-relationship-category.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-contact-relationship-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T13:42:57+00:00</t>
+    <t>2026-08-10T13:45:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-contact-relationship-category.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-contact-relationship-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T13:45:29+00:00</t>
+    <t>2026-08-10T13:54:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-contact-relationship-category.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-contact-relationship-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T13:54:17+00:00</t>
+    <t>2026-08-10T14:12:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-contact-relationship-category.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-contact-relationship-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T14:12:55+00:00</t>
+    <t>2026-08-10T14:29:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-contact-relationship-category.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-contact-relationship-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T14:29:18+00:00</t>
+    <t>2026-08-10T16:19:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-contact-relationship-category.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-contact-relationship-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T16:19:09+00:00</t>
+    <t>2026-08-10T16:22:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-contact-relationship-category.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-contact-relationship-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T16:22:30+00:00</t>
+    <t>2026-08-10T16:46:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-contact-relationship-category.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-contact-relationship-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T16:46:59+00:00</t>
+    <t>2026-08-11T07:24:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-contact-relationship-category.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-contact-relationship-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T07:24:13+00:00</t>
+    <t>2026-08-11T10:04:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-contact-relationship-category.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-contact-relationship-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T10:04:20+00:00</t>
+    <t>2026-08-11T11:39:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-contact-relationship-category.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-contact-relationship-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T11:39:02+00:00</t>
+    <t>2026-08-12T13:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-contact-relationship-category.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-contact-relationship-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T13:53:29+00:00</t>
+    <t>2026-08-12T14:08:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
